--- a/BE.xlsx
+++ b/BE.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dillonwalton/Desktop/business/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCFB999D-7B95-B546-ADB7-F193B9B15480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69742627-E481-9141-8CEC-59E4D968ECFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="760" windowWidth="17000" windowHeight="16940" activeTab="1" xr2:uid="{A9783F60-192C-EF49-B653-EB874A40C134}"/>
+    <workbookView xWindow="20" yWindow="760" windowWidth="26580" windowHeight="19540" activeTab="1" xr2:uid="{A9783F60-192C-EF49-B653-EB874A40C134}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
     <sheet name="Model" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -45,7 +45,7 @@
     <author>VAE Ventures</author>
   </authors>
   <commentList>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{ADE44D27-8ED5-8546-9775-6A086F0F5ABA}">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{ADE44D27-8ED5-8546-9775-6A086F0F5ABA}">
       <text>
         <r>
           <rPr>
@@ -118,10 +118,44 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>Dillon Walton</author>
     <author>VAE Ventures</author>
   </authors>
   <commentList>
-    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{A9D2441D-108E-2747-91C5-0397C0B969E2}">
+    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{5F610A5F-D63B-214C-A148-F86F272D8AFC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Dillon Walton:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Out of backlog -&gt; into production, producing for 24 hrs</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B18" authorId="1" shapeId="0" xr:uid="{A9D2441D-108E-2747-91C5-0397C0B969E2}">
       <text>
         <r>
           <rPr>
@@ -159,7 +193,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="123">
   <si>
     <t>Price</t>
   </si>
@@ -339,13 +373,204 @@
   </si>
   <si>
     <t>International headcount</t>
+  </si>
+  <si>
+    <t>Founded</t>
+  </si>
+  <si>
+    <t>CEO / Founder</t>
+  </si>
+  <si>
+    <t>KR Sridhar</t>
+  </si>
+  <si>
+    <t>First field trial deployed</t>
+  </si>
+  <si>
+    <t>Commercial launch</t>
+  </si>
+  <si>
+    <t>First microgrid online</t>
+  </si>
+  <si>
+    <t>US Manu Expansion</t>
+  </si>
+  <si>
+    <t>Global expansion (Japan)</t>
+  </si>
+  <si>
+    <t>First community microgrid</t>
+  </si>
+  <si>
+    <t>Public</t>
+  </si>
+  <si>
+    <t>Fremont,CA GW Facility</t>
+  </si>
+  <si>
+    <t>AEP 1GW of fuel cells</t>
+  </si>
+  <si>
+    <t>First hyperscaler agreement</t>
+  </si>
+  <si>
+    <t>Q423</t>
+  </si>
+  <si>
+    <t>Q323</t>
+  </si>
+  <si>
+    <t>Q223</t>
+  </si>
+  <si>
+    <t>Q123</t>
+  </si>
+  <si>
+    <t>Q422</t>
+  </si>
+  <si>
+    <t>Q322</t>
+  </si>
+  <si>
+    <t>Q222</t>
+  </si>
+  <si>
+    <t>Q122</t>
+  </si>
+  <si>
+    <t>Q421</t>
+  </si>
+  <si>
+    <t>Q321</t>
+  </si>
+  <si>
+    <t>Q221</t>
+  </si>
+  <si>
+    <t>Q121</t>
+  </si>
+  <si>
+    <t>Q420</t>
+  </si>
+  <si>
+    <t>Q320</t>
+  </si>
+  <si>
+    <t>Q220</t>
+  </si>
+  <si>
+    <t>Q120</t>
+  </si>
+  <si>
+    <t>Q419</t>
+  </si>
+  <si>
+    <t>Q319</t>
+  </si>
+  <si>
+    <t>Q219</t>
+  </si>
+  <si>
+    <t>Q119</t>
+  </si>
+  <si>
+    <t>Q218</t>
+  </si>
+  <si>
+    <t>Q318</t>
+  </si>
+  <si>
+    <t>Q418</t>
+  </si>
+  <si>
+    <t>Japan, India, South Korea</t>
+  </si>
+  <si>
+    <t>Install base (MW)</t>
+  </si>
+  <si>
+    <t>edge computing -&gt; in the end, will it always be edge?</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>Data centers</t>
+  </si>
+  <si>
+    <t>Enter SK</t>
+  </si>
+  <si>
+    <t>Scarce land, very high property values</t>
+  </si>
+  <si>
+    <t>Kelly Ayotte</t>
+  </si>
+  <si>
+    <t>Board member</t>
+  </si>
+  <si>
+    <t>John Chambers</t>
+  </si>
+  <si>
+    <t>50kW, 100kW</t>
+  </si>
+  <si>
+    <t>C&amp;I is focus, 1.6T market, 1M manufacturing
+Projected rate growth due to weather, DERs for speed, limited space (energy density is key)
+Data center / healthcare (demand for 24/7 power)</t>
+  </si>
+  <si>
+    <t>Acceptances</t>
+  </si>
+  <si>
+    <t>Acceptances (MW)</t>
+  </si>
+  <si>
+    <t>Randy Furr</t>
+  </si>
+  <si>
+    <t>CFO</t>
+  </si>
+  <si>
+    <t>Home Depot, AT&amp;T, Intel (25 / F100, 42 / F500)</t>
+  </si>
+  <si>
+    <t>Inventories</t>
+  </si>
+  <si>
+    <t>Prepaid Expense</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>PP&amp;E</t>
+  </si>
+  <si>
+    <t>Financing Recievable (ST)</t>
+  </si>
+  <si>
+    <t>Financing Recievable (LT)</t>
+  </si>
+  <si>
+    <t>Restricted cash (LT)</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>Deferred COGs (ST)</t>
+  </si>
+  <si>
+    <t>Quarter</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -387,13 +612,35 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FF0563C1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -409,7 +656,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -417,7 +664,18 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -440,15 +698,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
+      <xdr:col>35</xdr:col>
       <xdr:colOff>25400</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
+      <xdr:col>35</xdr:col>
       <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -492,6 +750,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -811,19 +1073,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D246C95D-561E-2848-93D4-760DA66CF86C}">
-  <dimension ref="E3:L8"/>
+  <dimension ref="B3:L36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="32.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="5:12" x14ac:dyDescent="0.2">
-      <c r="E3" s="3" t="s">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="D3" s="3" t="s">
         <v>38</v>
       </c>
+      <c r="E3" t="s">
+        <v>39</v>
+      </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="J3" t="s">
         <v>0</v>
@@ -832,11 +1097,11 @@
         <v>204.02</v>
       </c>
     </row>
-    <row r="4" spans="5:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="D4" t="s">
+        <v>40</v>
+      </c>
       <c r="E4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F4" t="s">
         <v>41</v>
       </c>
       <c r="J4" t="s">
@@ -849,7 +1114,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="5:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J5" t="s">
         <v>2</v>
       </c>
@@ -858,7 +1123,7 @@
         <v>60089469.130920008</v>
       </c>
     </row>
-    <row r="6" spans="5:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J6" t="s">
         <v>3</v>
       </c>
@@ -870,7 +1135,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="5:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J7" t="s">
         <v>4</v>
       </c>
@@ -882,13 +1147,159 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="5:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J8" t="s">
         <v>5</v>
       </c>
       <c r="K8" s="1">
         <f>K5-K6+K7</f>
         <v>60089249.571920007</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="D11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="D12" t="s">
+        <v>110</v>
+      </c>
+      <c r="E12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B14">
+        <v>2018</v>
+      </c>
+      <c r="D14" t="s">
+        <v>103</v>
+      </c>
+      <c r="E14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="D15" t="s">
+        <v>105</v>
+      </c>
+      <c r="E15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="25" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D25" s="7">
+        <v>2001</v>
+      </c>
+      <c r="E25" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D26" s="7">
+        <v>2006</v>
+      </c>
+      <c r="E26" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D27" s="7">
+        <v>2008</v>
+      </c>
+      <c r="E27" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D28" s="7">
+        <v>2011</v>
+      </c>
+      <c r="E28" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D29" s="7">
+        <v>2012</v>
+      </c>
+      <c r="E29" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D30" s="7">
+        <v>2013</v>
+      </c>
+      <c r="E30" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D31" s="7">
+        <v>2016</v>
+      </c>
+      <c r="E31" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="32" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D32" s="8">
+        <v>43070</v>
+      </c>
+      <c r="E32" t="s">
+        <v>101</v>
+      </c>
+      <c r="F32" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="33" spans="3:8" ht="153" x14ac:dyDescent="0.2">
+      <c r="C33" t="s">
+        <v>98</v>
+      </c>
+      <c r="D33" s="8">
+        <v>43282</v>
+      </c>
+      <c r="E33" t="s">
+        <v>69</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="G33" t="s">
+        <v>112</v>
+      </c>
+      <c r="H33" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="34" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="D34" s="7">
+        <v>2022</v>
+      </c>
+      <c r="E34" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="D35" s="7">
+        <v>2024</v>
+      </c>
+      <c r="E35" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="D36" s="7">
+        <v>2025</v>
+      </c>
+      <c r="E36" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -899,1294 +1310,2258 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1997143C-4B46-1145-8926-BC951BDCF94E}">
-  <dimension ref="B2:AK52"/>
+  <dimension ref="B2:BN108"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="22.1640625" customWidth="1"/>
+    <col min="2" max="2" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:37" x14ac:dyDescent="0.2">
-      <c r="C2" t="s">
+    <row r="2" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="C2" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="R2" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="S2" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="T2" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="U2" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="V2" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="W2" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="X2" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y2" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="AA2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="AB2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="AC2" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="AD2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="AE2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="I2" t="s">
+      <c r="AF2" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="AG2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="AH2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="AI2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="M2" t="s">
+      <c r="AJ2" t="s">
         <v>16</v>
       </c>
-      <c r="N2" t="s">
+      <c r="AK2" t="s">
         <v>17</v>
       </c>
-      <c r="O2" t="s">
+      <c r="AL2" t="s">
         <v>18</v>
       </c>
-      <c r="P2" t="s">
+      <c r="AM2" t="s">
         <v>19</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="AN2" t="s">
         <v>20</v>
       </c>
-      <c r="R2" t="s">
+      <c r="AO2" t="s">
         <v>21</v>
       </c>
-      <c r="U2">
+      <c r="AR2">
+        <v>2018</v>
+      </c>
+      <c r="AS2">
+        <v>2019</v>
+      </c>
+      <c r="AT2">
+        <v>2020</v>
+      </c>
+      <c r="AU2">
+        <v>2021</v>
+      </c>
+      <c r="AV2">
+        <v>2022</v>
+      </c>
+      <c r="AW2">
+        <v>2023</v>
+      </c>
+      <c r="AX2">
         <v>2024</v>
       </c>
-      <c r="V2">
+      <c r="AY2">
         <v>2025</v>
       </c>
-      <c r="W2">
+      <c r="AZ2">
         <v>2026</v>
       </c>
-      <c r="X2">
+      <c r="BA2">
         <v>2027</v>
       </c>
-      <c r="Y2">
+      <c r="BB2">
         <v>2028</v>
       </c>
-      <c r="Z2">
+      <c r="BC2">
         <v>2029</v>
       </c>
-      <c r="AA2">
+      <c r="BD2">
         <v>2030</v>
       </c>
-      <c r="AB2">
+      <c r="BE2">
         <v>2031</v>
       </c>
-      <c r="AC2">
+      <c r="BF2">
         <v>2032</v>
       </c>
-      <c r="AD2">
+      <c r="BG2">
         <v>2033</v>
       </c>
-      <c r="AE2">
+      <c r="BH2">
         <v>2034</v>
       </c>
-      <c r="AF2">
+      <c r="BI2">
         <v>2035</v>
       </c>
-      <c r="AG2">
+      <c r="BJ2">
         <v>2036</v>
       </c>
-      <c r="AH2">
+      <c r="BK2">
         <v>2037</v>
       </c>
-      <c r="AI2">
+      <c r="BL2">
         <v>2038</v>
       </c>
-      <c r="AJ2">
+      <c r="BM2">
         <v>2039</v>
       </c>
-      <c r="AK2">
+      <c r="BN2">
         <v>2040</v>
       </c>
     </row>
-    <row r="5" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="2:66" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="8" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="9" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9">
+        <v>18.100000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="2:37" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
+    <row r="13" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
         <v>58</v>
       </c>
-      <c r="J6">
+      <c r="AG13">
         <v>1752</v>
       </c>
     </row>
-    <row r="7" spans="2:37" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
+    <row r="14" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
         <v>42</v>
       </c>
-      <c r="J7">
+      <c r="AG14">
         <v>2214</v>
       </c>
     </row>
-    <row r="8" spans="2:37" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
+    <row r="15" spans="2:66" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
         <v>43</v>
       </c>
-      <c r="J8">
+      <c r="AG15">
         <v>1100</v>
       </c>
     </row>
-    <row r="10" spans="2:37" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
+    <row r="17" spans="2:35" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="2:37" x14ac:dyDescent="0.2">
-      <c r="B11" t="s">
+    <row r="18" spans="2:35" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="2:37" x14ac:dyDescent="0.2">
-      <c r="B12" t="s">
+    <row r="19" spans="2:35" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
         <v>44</v>
       </c>
-      <c r="J12">
+      <c r="AG19">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="2:37" x14ac:dyDescent="0.2">
-      <c r="B14" t="s">
+    <row r="21" spans="2:35" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="2:37" x14ac:dyDescent="0.2">
-      <c r="B15" t="s">
+    <row r="22" spans="2:35" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="2:37" x14ac:dyDescent="0.2">
-      <c r="B16" t="s">
+    <row r="23" spans="2:35" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B21" t="s">
+    <row r="28" spans="2:35" x14ac:dyDescent="0.2">
+      <c r="B28" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="2">
-        <f>C26/C$30</f>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="2"/>
+      <c r="W28" s="2"/>
+      <c r="X28" s="2"/>
+      <c r="Y28" s="2"/>
+      <c r="Z28" s="2">
+        <f>Z33/Z$37</f>
         <v>0.65178624552694886</v>
       </c>
-      <c r="D21" s="2">
-        <f t="shared" ref="D21:L21" si="0">D26/D$30</f>
+      <c r="AA28" s="2">
+        <f t="shared" ref="AA28:AI28" si="0">AA33/AA$37</f>
         <v>0.67400310334249647</v>
       </c>
-      <c r="E21" s="2">
+      <c r="AB28" s="2">
         <f t="shared" si="0"/>
         <v>0.70744210819382403</v>
       </c>
-      <c r="F21" s="2">
+      <c r="AC28" s="2">
         <f t="shared" si="0"/>
         <v>0.82410336953806207</v>
       </c>
-      <c r="G21" s="2">
+      <c r="AD28" s="2">
         <f t="shared" si="0"/>
         <v>0.6498630456320299</v>
       </c>
-      <c r="H21" s="2">
+      <c r="AE28" s="2">
         <f t="shared" si="0"/>
         <v>0.73923218406846736</v>
       </c>
-      <c r="I21" s="2">
+      <c r="AF28" s="2">
         <f t="shared" si="0"/>
         <v>0.74042092446170682</v>
       </c>
-      <c r="J21" s="2">
+      <c r="AG28" s="2">
         <f t="shared" si="0"/>
         <v>0.82101190330764584</v>
       </c>
-      <c r="K21" s="2">
+      <c r="AH28" s="2">
         <f t="shared" si="0"/>
         <v>0.8699081557384688</v>
       </c>
-      <c r="L21" s="2">
+      <c r="AI28" s="2">
         <f t="shared" si="0"/>
         <v>0.87802114768178041</v>
       </c>
     </row>
-    <row r="22" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B22" t="s">
+    <row r="29" spans="2:35" x14ac:dyDescent="0.2">
+      <c r="B29" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="2">
-        <f t="shared" ref="C22:L24" si="1">C27/C$30</f>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="2"/>
+      <c r="T29" s="2"/>
+      <c r="U29" s="2"/>
+      <c r="V29" s="2"/>
+      <c r="W29" s="2"/>
+      <c r="X29" s="2"/>
+      <c r="Y29" s="2"/>
+      <c r="Z29" s="2">
+        <f t="shared" ref="Z29:AI31" si="1">Z34/Z$37</f>
         <v>4.8636197502741209E-2</v>
       </c>
-      <c r="D22" s="2">
+      <c r="AA29" s="2">
         <f t="shared" si="1"/>
         <v>0.12726980316707717</v>
       </c>
-      <c r="E22" s="2">
+      <c r="AB29" s="2">
         <f t="shared" si="1"/>
         <v>9.6996767984893054E-2</v>
       </c>
-      <c r="F22" s="2">
+      <c r="AC29" s="2">
         <f t="shared" si="1"/>
         <v>6.3049338478982087E-2</v>
       </c>
-      <c r="G22" s="2">
+      <c r="AD29" s="2">
         <f t="shared" si="1"/>
         <v>0.10321727741464509</v>
       </c>
-      <c r="H22" s="2">
+      <c r="AE29" s="2">
         <f t="shared" si="1"/>
         <v>9.3140797822760329E-2</v>
       </c>
-      <c r="I22" s="2">
+      <c r="AF29" s="2">
         <f t="shared" si="1"/>
         <v>0.12671853084878468</v>
       </c>
-      <c r="J22" s="2">
+      <c r="AG29" s="2">
         <f t="shared" si="1"/>
         <v>8.6503112450702926E-2</v>
       </c>
-      <c r="K22" s="2">
+      <c r="AH29" s="2">
         <f t="shared" si="1"/>
         <v>3.4526145922929644E-2</v>
       </c>
-      <c r="L22" s="2">
+      <c r="AI29" s="2">
         <f t="shared" si="1"/>
         <v>4.785026727928926E-2</v>
       </c>
     </row>
-    <row r="23" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B23" t="s">
+    <row r="30" spans="2:35" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
         <v>51</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="2"/>
+      <c r="T30" s="2"/>
+      <c r="U30" s="2"/>
+      <c r="V30" s="2"/>
+      <c r="W30" s="2"/>
+      <c r="X30" s="2"/>
+      <c r="Y30" s="2"/>
+      <c r="Z30" s="2">
         <f t="shared" si="1"/>
         <v>0.23995104080782667</v>
       </c>
-      <c r="D23" s="2">
+      <c r="AA30" s="2">
         <f t="shared" si="1"/>
         <v>0.15645075305196759</v>
       </c>
-      <c r="E23" s="2">
+      <c r="AB30" s="2">
         <f t="shared" si="1"/>
         <v>0.15361453075256321</v>
       </c>
-      <c r="F23" s="2">
+      <c r="AC30" s="2">
         <f t="shared" si="1"/>
         <v>9.3973895557772358E-2</v>
       </c>
-      <c r="G23" s="2">
+      <c r="AD30" s="2">
         <f t="shared" si="1"/>
         <v>0.16424708837774257</v>
       </c>
-      <c r="H23" s="2">
+      <c r="AE30" s="2">
         <f t="shared" si="1"/>
         <v>0.13570114793565977</v>
       </c>
-      <c r="I23" s="2">
+      <c r="AF30" s="2">
         <f t="shared" si="1"/>
         <v>0.11291248593579013</v>
       </c>
-      <c r="J23" s="2">
+      <c r="AG30" s="2">
         <f t="shared" si="1"/>
         <v>7.9326666520934633E-2</v>
       </c>
-      <c r="K23" s="2">
+      <c r="AH30" s="2">
         <f t="shared" si="1"/>
         <v>8.2389548554431508E-2</v>
       </c>
-      <c r="L23" s="2">
+      <c r="AI30" s="2">
         <f t="shared" si="1"/>
         <v>6.4788124257883439E-2</v>
       </c>
     </row>
-    <row r="24" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B24" t="s">
+    <row r="31" spans="2:35" x14ac:dyDescent="0.2">
+      <c r="B31" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="2"/>
+      <c r="T31" s="2"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="2"/>
+      <c r="W31" s="2"/>
+      <c r="X31" s="2"/>
+      <c r="Y31" s="2"/>
+      <c r="Z31" s="2">
         <f t="shared" si="1"/>
         <v>5.9626516162483316E-2</v>
       </c>
-      <c r="D24" s="2">
+      <c r="AA31" s="2">
         <f t="shared" si="1"/>
         <v>4.2276340438458813E-2</v>
       </c>
-      <c r="E24" s="2">
+      <c r="AB31" s="2">
         <f t="shared" si="1"/>
         <v>4.1946593068719659E-2</v>
       </c>
-      <c r="F24" s="2">
+      <c r="AC31" s="2">
         <f t="shared" si="1"/>
         <v>1.8873396425183396E-2</v>
       </c>
-      <c r="G24" s="2">
+      <c r="AD31" s="2">
         <f t="shared" si="1"/>
         <v>8.2672588575582559E-2</v>
       </c>
-      <c r="H24" s="2">
+      <c r="AE31" s="2">
         <f t="shared" si="1"/>
         <v>3.1925870173112485E-2</v>
       </c>
-      <c r="I24" s="2">
+      <c r="AF31" s="2">
         <f t="shared" si="1"/>
         <v>1.9948058753718346E-2</v>
       </c>
-      <c r="J24" s="2">
+      <c r="AG31" s="2">
         <f t="shared" si="1"/>
         <v>1.315831772071654E-2</v>
       </c>
-      <c r="K24" s="2">
+      <c r="AH31" s="2">
         <f t="shared" si="1"/>
         <v>1.3176149784169981E-2</v>
       </c>
-      <c r="L24" s="2">
+      <c r="AI31" s="2">
         <f t="shared" si="1"/>
         <v>9.3404607810468714E-3</v>
       </c>
     </row>
-    <row r="26" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B26" t="s">
+    <row r="33" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C33" s="1">
+        <v>108.654</v>
+      </c>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1"/>
+      <c r="V33" s="1"/>
+      <c r="W33" s="1"/>
+      <c r="X33" s="1"/>
+      <c r="Y33" s="1"/>
+      <c r="Z33" s="1">
         <v>153.364</v>
       </c>
-      <c r="D26" s="1">
+      <c r="AA33" s="1">
         <v>226.30799999999999</v>
       </c>
-      <c r="E26" s="1">
+      <c r="AB33" s="1">
         <v>233.77</v>
       </c>
-      <c r="F26" s="1">
+      <c r="AC33" s="1">
         <v>471.71100000000001</v>
       </c>
-      <c r="G26" s="1">
+      <c r="AD33" s="1">
         <v>211.869</v>
       </c>
-      <c r="H26" s="1">
+      <c r="AE33" s="1">
         <v>296.61099999999999</v>
       </c>
-      <c r="I26" s="1">
+      <c r="AF33" s="1">
         <v>384.31400000000002</v>
       </c>
-      <c r="J26" s="1">
+      <c r="AG33" s="1">
         <v>638.48699999999997</v>
       </c>
-      <c r="K26" s="1">
+      <c r="AH33" s="1">
         <v>653.34799999999996</v>
       </c>
-      <c r="L26" s="1">
+      <c r="AI33" s="1">
         <v>935.41300000000001</v>
       </c>
-      <c r="U26" s="1">
-        <f>SUM(C26:F26)</f>
+      <c r="AX33" s="1">
+        <f>SUM(Z33:AC33)</f>
         <v>1085.153</v>
       </c>
-      <c r="V26" s="1">
-        <f>SUM(G26:J26)</f>
+      <c r="AY33" s="1">
+        <f>SUM(AD33:AG33)</f>
         <v>1531.2809999999999</v>
       </c>
     </row>
-    <row r="27" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B27" t="s">
+    <row r="34" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="B34" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C34" s="1">
+        <v>26.245000000000001</v>
+      </c>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="1"/>
+      <c r="V34" s="1"/>
+      <c r="W34" s="1"/>
+      <c r="X34" s="1"/>
+      <c r="Y34" s="1"/>
+      <c r="Z34" s="1">
         <v>11.444000000000001</v>
       </c>
-      <c r="D27" s="1">
+      <c r="AA34" s="1">
         <v>42.732999999999997</v>
       </c>
-      <c r="E27" s="1">
+      <c r="AB34" s="1">
         <v>32.052</v>
       </c>
-      <c r="F27" s="1">
+      <c r="AC34" s="1">
         <v>36.088999999999999</v>
       </c>
-      <c r="G27" s="1">
+      <c r="AD34" s="1">
         <v>33.651000000000003</v>
       </c>
-      <c r="H27" s="1">
+      <c r="AE34" s="1">
         <v>37.372</v>
       </c>
-      <c r="I27" s="1">
+      <c r="AF34" s="1">
         <v>65.772999999999996</v>
       </c>
-      <c r="J27" s="1">
+      <c r="AG34" s="1">
         <v>67.272000000000006</v>
       </c>
-      <c r="K27" s="1">
+      <c r="AH34" s="1">
         <v>25.931000000000001</v>
       </c>
-      <c r="L27" s="1">
+      <c r="AI34" s="1">
         <v>50.978000000000002</v>
       </c>
-      <c r="U27" s="1">
-        <f t="shared" ref="U27:U30" si="2">SUM(C27:F27)</f>
+      <c r="AX34" s="1">
+        <f t="shared" ref="AX34:AX37" si="2">SUM(Z34:AC34)</f>
         <v>122.318</v>
       </c>
-      <c r="V27" s="1">
-        <f t="shared" ref="V27:V30" si="3">SUM(G27:J27)</f>
+      <c r="AY34" s="1">
+        <f t="shared" ref="AY34:AY37" si="3">SUM(AD34:AG34)</f>
         <v>204.06799999999998</v>
       </c>
     </row>
-    <row r="28" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B28" t="s">
+    <row r="35" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="B35" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C35" s="1">
+        <v>19.975000000000001</v>
+      </c>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
+      <c r="Q35" s="1"/>
+      <c r="R35" s="1"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="1"/>
+      <c r="U35" s="1"/>
+      <c r="V35" s="1"/>
+      <c r="W35" s="1"/>
+      <c r="X35" s="1"/>
+      <c r="Y35" s="1"/>
+      <c r="Z35" s="1">
         <v>56.46</v>
       </c>
-      <c r="D28" s="1">
+      <c r="AA35" s="1">
         <v>52.530999999999999</v>
       </c>
-      <c r="E28" s="1">
+      <c r="AB35" s="1">
         <v>50.761000000000003</v>
       </c>
-      <c r="F28" s="1">
+      <c r="AC35" s="1">
         <v>53.79</v>
       </c>
-      <c r="G28" s="1">
+      <c r="AD35" s="1">
         <v>53.548000000000002</v>
       </c>
-      <c r="H28" s="1">
+      <c r="AE35" s="1">
         <v>54.448999999999998</v>
       </c>
-      <c r="I28" s="1">
+      <c r="AF35" s="1">
         <v>58.606999999999999</v>
       </c>
-      <c r="J28" s="1">
+      <c r="AG35" s="1">
         <v>61.691000000000003</v>
       </c>
-      <c r="K28" s="1">
+      <c r="AH35" s="1">
         <v>61.878999999999998</v>
       </c>
-      <c r="L28" s="1">
+      <c r="AI35" s="1">
         <v>69.022999999999996</v>
       </c>
-      <c r="U28" s="1">
+      <c r="AX35" s="1">
         <f t="shared" si="2"/>
         <v>213.542</v>
       </c>
-      <c r="V28" s="1">
+      <c r="AY35" s="1">
         <f t="shared" si="3"/>
         <v>228.29499999999999</v>
       </c>
     </row>
-    <row r="29" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B29" t="s">
+    <row r="36" spans="2:51" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C36" s="1">
+        <v>14.007</v>
+      </c>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
+      <c r="Q36" s="1"/>
+      <c r="R36" s="1"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="1"/>
+      <c r="U36" s="1"/>
+      <c r="V36" s="1"/>
+      <c r="W36" s="1"/>
+      <c r="X36" s="1"/>
+      <c r="Y36" s="1"/>
+      <c r="Z36" s="1">
         <v>14.03</v>
       </c>
-      <c r="D29" s="1">
+      <c r="AA36" s="1">
         <v>14.195</v>
       </c>
-      <c r="E29" s="1">
+      <c r="AB36" s="1">
         <v>13.861000000000001</v>
       </c>
-      <c r="F29" s="1">
+      <c r="AC36" s="1">
         <v>10.803000000000001</v>
       </c>
-      <c r="G29" s="1">
+      <c r="AD36" s="1">
         <v>26.952999999999999</v>
       </c>
-      <c r="H29" s="1">
+      <c r="AE36" s="1">
         <v>12.81</v>
       </c>
-      <c r="I29" s="1">
+      <c r="AF36" s="1">
         <v>10.353999999999999</v>
       </c>
-      <c r="J29" s="1">
+      <c r="AG36" s="1">
         <v>10.233000000000001</v>
       </c>
-      <c r="K29" s="1">
+      <c r="AH36" s="1">
         <v>9.8960000000000008</v>
       </c>
-      <c r="L29" s="1">
+      <c r="AI36" s="1">
         <v>9.9510000000000005</v>
       </c>
-      <c r="U29" s="1">
+      <c r="AX36" s="1">
         <f t="shared" si="2"/>
         <v>52.888999999999996</v>
       </c>
-      <c r="V29" s="1">
+      <c r="AY36" s="1">
         <f t="shared" si="3"/>
         <v>60.349999999999994</v>
       </c>
     </row>
-    <row r="30" spans="2:22" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="3" t="s">
+    <row r="37" spans="2:51" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="4">
-        <f>SUM(C26:C29)</f>
+      <c r="C37" s="4">
+        <f>SUM(C33:C36)</f>
+        <v>168.881</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
+      <c r="N37" s="4"/>
+      <c r="O37" s="4"/>
+      <c r="P37" s="4"/>
+      <c r="Q37" s="4"/>
+      <c r="R37" s="4"/>
+      <c r="S37" s="4"/>
+      <c r="T37" s="4"/>
+      <c r="U37" s="4"/>
+      <c r="V37" s="4"/>
+      <c r="W37" s="4"/>
+      <c r="X37" s="4"/>
+      <c r="Y37" s="4"/>
+      <c r="Z37" s="4">
+        <f t="shared" ref="Z37:AI37" si="4">SUM(Z33:Z36)</f>
         <v>235.298</v>
       </c>
-      <c r="D30" s="4">
-        <f>SUM(D26:D29)</f>
+      <c r="AA37" s="4">
+        <f t="shared" si="4"/>
         <v>335.767</v>
       </c>
-      <c r="E30" s="4">
-        <f>SUM(E26:E29)</f>
+      <c r="AB37" s="4">
+        <f t="shared" si="4"/>
         <v>330.44400000000002</v>
       </c>
-      <c r="F30" s="4">
-        <f>SUM(F26:F29)</f>
+      <c r="AC37" s="4">
+        <f t="shared" si="4"/>
         <v>572.39300000000003</v>
       </c>
-      <c r="G30" s="4">
-        <f>SUM(G26:G29)</f>
+      <c r="AD37" s="4">
+        <f t="shared" si="4"/>
         <v>326.02099999999996</v>
       </c>
-      <c r="H30" s="4">
-        <f>SUM(H26:H29)</f>
+      <c r="AE37" s="4">
+        <f t="shared" si="4"/>
         <v>401.24200000000002</v>
       </c>
-      <c r="I30" s="4">
-        <f>SUM(I26:I29)</f>
+      <c r="AF37" s="4">
+        <f t="shared" si="4"/>
         <v>519.048</v>
       </c>
-      <c r="J30" s="4">
-        <f>SUM(J26:J29)</f>
+      <c r="AG37" s="4">
+        <f t="shared" si="4"/>
         <v>777.68299999999999</v>
       </c>
-      <c r="K30" s="4">
-        <f>SUM(K26:K29)</f>
+      <c r="AH37" s="4">
+        <f t="shared" si="4"/>
         <v>751.05399999999997</v>
       </c>
-      <c r="L30" s="4">
-        <f>SUM(L26:L29)</f>
+      <c r="AI37" s="4">
+        <f t="shared" si="4"/>
         <v>1065.365</v>
       </c>
-      <c r="U30" s="4">
+      <c r="AX37" s="4">
         <f t="shared" si="2"/>
         <v>1473.902</v>
       </c>
-      <c r="V30" s="4">
+      <c r="AY37" s="4">
         <f t="shared" si="3"/>
         <v>2023.9939999999999</v>
       </c>
     </row>
-    <row r="31" spans="2:22" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="4"/>
-    </row>
-    <row r="32" spans="2:22" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="6" t="s">
+    <row r="38" spans="2:51" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
+      <c r="N38" s="4"/>
+      <c r="O38" s="4"/>
+      <c r="P38" s="4"/>
+      <c r="Q38" s="4"/>
+      <c r="R38" s="4"/>
+      <c r="S38" s="4"/>
+      <c r="T38" s="4"/>
+      <c r="U38" s="4"/>
+      <c r="V38" s="4"/>
+      <c r="W38" s="4"/>
+      <c r="X38" s="4"/>
+      <c r="Y38" s="4"/>
+      <c r="Z38" s="4"/>
+      <c r="AA38" s="4"/>
+      <c r="AB38" s="4"/>
+      <c r="AC38" s="4"/>
+      <c r="AD38" s="4"/>
+      <c r="AE38" s="4"/>
+      <c r="AF38" s="4"/>
+      <c r="AG38" s="4"/>
+      <c r="AH38" s="4"/>
+      <c r="AI38" s="4"/>
+    </row>
+    <row r="39" spans="2:51" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="5">
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="5"/>
+      <c r="R39" s="5"/>
+      <c r="S39" s="5"/>
+      <c r="T39" s="5"/>
+      <c r="U39" s="5"/>
+      <c r="V39" s="5"/>
+      <c r="W39" s="5"/>
+      <c r="X39" s="5"/>
+      <c r="Y39" s="5"/>
+      <c r="Z39" s="5">
         <v>115.75700000000001</v>
       </c>
-      <c r="D32" s="5">
+      <c r="AA39" s="5">
         <v>161.33199999999999</v>
       </c>
-      <c r="E32" s="5">
+      <c r="AB39" s="5">
         <v>155.124</v>
       </c>
-      <c r="F32" s="5">
+      <c r="AC39" s="5">
         <v>253.63399999999999</v>
       </c>
-      <c r="G32" s="5">
+      <c r="AD39" s="5">
         <v>139.57300000000001</v>
       </c>
-      <c r="H32" s="5">
+      <c r="AE39" s="5">
         <v>198.74600000000001</v>
       </c>
-      <c r="I32" s="5">
+      <c r="AF39" s="5">
         <v>249.79400000000001</v>
       </c>
-      <c r="J32" s="5">
+      <c r="AG39" s="5">
         <v>404.72800000000001</v>
       </c>
-      <c r="K32" s="5">
+      <c r="AH39" s="5">
         <v>429.23200000000003</v>
       </c>
-      <c r="L32" s="5">
+      <c r="AI39" s="5">
         <v>593.95699999999999</v>
       </c>
-      <c r="U32" s="1">
-        <f>SUM(C32:F32)</f>
+      <c r="AX39" s="1">
+        <f>SUM(Z39:AC39)</f>
         <v>685.84699999999998</v>
       </c>
     </row>
-    <row r="33" spans="2:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B33" t="s">
+    <row r="40" spans="2:51" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B40" t="s">
         <v>27</v>
       </c>
-      <c r="C33" s="5">
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5"/>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="5"/>
+      <c r="R40" s="5"/>
+      <c r="S40" s="5"/>
+      <c r="T40" s="5"/>
+      <c r="U40" s="5"/>
+      <c r="V40" s="5"/>
+      <c r="W40" s="5"/>
+      <c r="X40" s="5"/>
+      <c r="Y40" s="5"/>
+      <c r="Z40" s="5">
         <v>15.353</v>
       </c>
-      <c r="D33" s="5">
+      <c r="AA40" s="5">
         <v>44.298000000000002</v>
       </c>
-      <c r="E33" s="5">
+      <c r="AB40" s="5">
         <v>35.688000000000002</v>
       </c>
-      <c r="F33" s="5">
+      <c r="AC40" s="5">
         <v>34.106999999999999</v>
       </c>
-      <c r="G33" s="5">
+      <c r="AD40" s="5">
         <v>33.314999999999998</v>
       </c>
-      <c r="H33" s="5">
+      <c r="AE40" s="5">
         <v>38.223999999999997</v>
       </c>
-      <c r="I33" s="5">
+      <c r="AF40" s="5">
         <v>59.920999999999999</v>
       </c>
-      <c r="J33" s="5">
+      <c r="AG40" s="5">
         <v>74.486000000000004</v>
       </c>
-      <c r="K33" s="5">
+      <c r="AH40" s="5">
         <v>35.08</v>
       </c>
-      <c r="L33" s="5">
+      <c r="AI40" s="5">
         <v>52.829000000000001</v>
       </c>
-      <c r="U33" s="1">
-        <f t="shared" ref="U33:U36" si="4">SUM(C33:F33)</f>
+      <c r="AX40" s="1">
+        <f t="shared" ref="AX40:AX43" si="5">SUM(Z40:AC40)</f>
         <v>129.446</v>
       </c>
     </row>
-    <row r="34" spans="2:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B34" t="s">
+    <row r="41" spans="2:51" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B41" t="s">
         <v>28</v>
       </c>
-      <c r="C34" s="5">
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="5"/>
+      <c r="R41" s="5"/>
+      <c r="S41" s="5"/>
+      <c r="T41" s="5"/>
+      <c r="U41" s="5"/>
+      <c r="V41" s="5"/>
+      <c r="W41" s="5"/>
+      <c r="X41" s="5"/>
+      <c r="Y41" s="5"/>
+      <c r="Z41" s="5">
         <v>56.506</v>
       </c>
-      <c r="D34" s="5">
+      <c r="AA41" s="5">
         <v>52.401000000000003</v>
       </c>
-      <c r="E34" s="5">
+      <c r="AB41" s="5">
         <v>51.363</v>
       </c>
-      <c r="F34" s="5">
+      <c r="AC41" s="5">
         <v>54.691000000000003</v>
       </c>
-      <c r="G34" s="5">
+      <c r="AD41" s="5">
         <v>52.857999999999997</v>
       </c>
-      <c r="H34" s="5">
+      <c r="AE41" s="5">
         <v>49.408000000000001</v>
       </c>
-      <c r="I34" s="5">
+      <c r="AF41" s="5">
         <v>51.834000000000003</v>
       </c>
-      <c r="J34" s="5">
+      <c r="AG41" s="5">
         <v>51.289000000000001</v>
       </c>
-      <c r="K34" s="5">
+      <c r="AH41" s="5">
         <v>53.664000000000001</v>
       </c>
-      <c r="L34" s="5">
+      <c r="AI41" s="5">
         <v>56.148000000000003</v>
       </c>
-      <c r="U34" s="1">
-        <f t="shared" si="4"/>
+      <c r="AX41" s="1">
+        <f t="shared" si="5"/>
         <v>214.96100000000001</v>
       </c>
     </row>
-    <row r="35" spans="2:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B35" t="s">
+    <row r="42" spans="2:51" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B42" t="s">
         <v>29</v>
       </c>
-      <c r="C35" s="5">
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="5"/>
+      <c r="P42" s="5"/>
+      <c r="Q42" s="5"/>
+      <c r="R42" s="5"/>
+      <c r="S42" s="5"/>
+      <c r="T42" s="5"/>
+      <c r="U42" s="5"/>
+      <c r="V42" s="5"/>
+      <c r="W42" s="5"/>
+      <c r="X42" s="5"/>
+      <c r="Y42" s="5"/>
+      <c r="Z42" s="5">
         <v>9.6059999999999999</v>
       </c>
-      <c r="D35" s="5">
+      <c r="AA42" s="5">
         <v>9.2140000000000004</v>
       </c>
-      <c r="E35" s="5">
+      <c r="AB42" s="5">
         <v>9.49</v>
       </c>
-      <c r="F35" s="5">
+      <c r="AC42" s="5">
         <v>10.644</v>
       </c>
-      <c r="G35" s="5">
+      <c r="AD42" s="5">
         <v>11.568</v>
       </c>
-      <c r="H35" s="5">
+      <c r="AE42" s="5">
         <v>7.7409999999999997</v>
       </c>
-      <c r="I35" s="5">
+      <c r="AF42" s="5">
         <v>5.8239999999999998</v>
       </c>
-      <c r="J35" s="5">
+      <c r="AG42" s="5">
         <v>7.2850000000000001</v>
       </c>
-      <c r="K35" s="5">
+      <c r="AH42" s="5">
         <v>7.5339999999999998</v>
       </c>
-      <c r="L35" s="5">
+      <c r="AI42" s="5">
         <v>6.859</v>
       </c>
-      <c r="U35" s="1">
-        <f t="shared" si="4"/>
+      <c r="AX42" s="1">
+        <f t="shared" si="5"/>
         <v>38.954000000000001</v>
       </c>
     </row>
-    <row r="36" spans="2:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="3" t="s">
+    <row r="43" spans="2:51" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B43" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C36" s="4">
-        <f>C30-SUM(C32:C35)</f>
+      <c r="C43" s="4">
+        <f>C37-136.11</f>
+        <v>32.770999999999987</v>
+      </c>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="4"/>
+      <c r="N43" s="4"/>
+      <c r="O43" s="4"/>
+      <c r="P43" s="4"/>
+      <c r="Q43" s="4"/>
+      <c r="R43" s="4"/>
+      <c r="S43" s="4"/>
+      <c r="T43" s="4"/>
+      <c r="U43" s="4"/>
+      <c r="V43" s="4"/>
+      <c r="W43" s="4"/>
+      <c r="X43" s="4"/>
+      <c r="Y43" s="4"/>
+      <c r="Z43" s="4">
+        <f t="shared" ref="Z43:AG43" si="6">Z37-SUM(Z39:Z42)</f>
         <v>38.075999999999993</v>
       </c>
-      <c r="D36" s="4">
-        <f>D30-SUM(D32:D35)</f>
+      <c r="AA43" s="4">
+        <f t="shared" si="6"/>
         <v>68.521999999999991</v>
       </c>
-      <c r="E36" s="4">
-        <f>E30-SUM(E32:E35)</f>
+      <c r="AB43" s="4">
+        <f t="shared" si="6"/>
         <v>78.778999999999996</v>
       </c>
-      <c r="F36" s="4">
-        <f>F30-SUM(F32:F35)</f>
+      <c r="AC43" s="4">
+        <f t="shared" si="6"/>
         <v>219.31700000000001</v>
       </c>
-      <c r="G36" s="4">
-        <f>G30-SUM(G32:G35)</f>
+      <c r="AD43" s="4">
+        <f t="shared" si="6"/>
         <v>88.706999999999937</v>
       </c>
-      <c r="H36" s="4">
-        <f>H30-SUM(H32:H35)</f>
+      <c r="AE43" s="4">
+        <f t="shared" si="6"/>
         <v>107.12300000000005</v>
       </c>
-      <c r="I36" s="4">
-        <f>I30-SUM(I32:I35)</f>
+      <c r="AF43" s="4">
+        <f t="shared" si="6"/>
         <v>151.67499999999995</v>
       </c>
-      <c r="J36" s="4">
-        <f>J30-SUM(J32:J35)</f>
+      <c r="AG43" s="4">
+        <f t="shared" si="6"/>
         <v>239.89499999999998</v>
       </c>
-      <c r="K36" s="4">
-        <f t="shared" ref="K36:L36" si="5">K30-SUM(K32:K35)</f>
+      <c r="AH43" s="4">
+        <f t="shared" ref="AH43:AI43" si="7">AH37-SUM(AH39:AH42)</f>
         <v>225.54399999999998</v>
       </c>
-      <c r="L36" s="4">
+      <c r="AI43" s="4">
+        <f t="shared" si="7"/>
+        <v>355.572</v>
+      </c>
+      <c r="AX43" s="4">
         <f t="shared" si="5"/>
-        <v>355.572</v>
-      </c>
-      <c r="U36" s="4">
-        <f t="shared" si="4"/>
         <v>404.69399999999996</v>
       </c>
     </row>
-    <row r="37" spans="2:21" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="6" t="s">
+    <row r="44" spans="2:51" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C37" s="5">
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="5"/>
+      <c r="P44" s="5"/>
+      <c r="Q44" s="5"/>
+      <c r="R44" s="5"/>
+      <c r="S44" s="5"/>
+      <c r="T44" s="5"/>
+      <c r="U44" s="5"/>
+      <c r="V44" s="5"/>
+      <c r="W44" s="5"/>
+      <c r="X44" s="5"/>
+      <c r="Y44" s="5"/>
+      <c r="Z44" s="5">
         <v>35.484999999999999</v>
       </c>
-      <c r="D37" s="5">
+      <c r="AA44" s="5">
         <v>37.363999999999997</v>
       </c>
-      <c r="E37" s="5">
+      <c r="AB44" s="5">
         <v>36.314999999999998</v>
       </c>
-      <c r="F37" s="5">
+      <c r="AC44" s="5">
         <v>39.465000000000003</v>
       </c>
-      <c r="G37" s="5">
+      <c r="AD44" s="5">
         <v>40.612000000000002</v>
       </c>
-      <c r="H37" s="5">
+      <c r="AE44" s="5">
         <v>40.768000000000001</v>
       </c>
-      <c r="I37" s="5">
+      <c r="AF44" s="5">
         <v>48.723999999999997</v>
       </c>
-      <c r="J37" s="5">
+      <c r="AG44" s="5">
         <v>55.889000000000003</v>
       </c>
-      <c r="K37" s="5">
+      <c r="AH44" s="5">
         <f>56.849</f>
         <v>56.848999999999997</v>
       </c>
-      <c r="L37" s="5">
+      <c r="AI44" s="5">
         <v>58.872999999999998</v>
       </c>
-      <c r="U37" s="1">
-        <f>SUM(C37:F37)</f>
+      <c r="AX44" s="1">
+        <f>SUM(Z44:AC44)</f>
         <v>148.62899999999999</v>
       </c>
     </row>
-    <row r="38" spans="2:21" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="6" t="s">
+    <row r="45" spans="2:51" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C38" s="5">
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="5"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="5"/>
+      <c r="P45" s="5"/>
+      <c r="Q45" s="5"/>
+      <c r="R45" s="5"/>
+      <c r="S45" s="5"/>
+      <c r="T45" s="5"/>
+      <c r="U45" s="5"/>
+      <c r="V45" s="5"/>
+      <c r="W45" s="5"/>
+      <c r="X45" s="5"/>
+      <c r="Y45" s="5"/>
+      <c r="Z45" s="5">
         <v>13.599</v>
       </c>
-      <c r="D38" s="5">
+      <c r="AA45" s="5">
         <v>17.901</v>
       </c>
-      <c r="E38" s="5">
+      <c r="AB45" s="5">
         <v>14.667</v>
       </c>
-      <c r="F38" s="5">
+      <c r="AC45" s="5">
         <v>21.838000000000001</v>
       </c>
-      <c r="G38" s="5">
+      <c r="AD45" s="5">
         <v>22.265000000000001</v>
       </c>
-      <c r="H38" s="5">
+      <c r="AE45" s="5">
         <v>24.065999999999999</v>
       </c>
-      <c r="I38" s="5">
+      <c r="AF45" s="5">
         <v>41.994999999999997</v>
       </c>
-      <c r="J38" s="5">
+      <c r="AG45" s="5">
         <v>41.902000000000001</v>
       </c>
-      <c r="K38" s="5">
+      <c r="AH45" s="5">
         <v>38.439</v>
       </c>
-      <c r="L38" s="5">
+      <c r="AI45" s="5">
         <v>43.045000000000002</v>
       </c>
-      <c r="U38" s="1">
-        <f t="shared" ref="U38:U41" si="6">SUM(C38:F38)</f>
+      <c r="AX45" s="1">
+        <f t="shared" ref="AX45:AX48" si="8">SUM(Z45:AC45)</f>
         <v>68.004999999999995</v>
       </c>
     </row>
-    <row r="39" spans="2:21" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="6" t="s">
+    <row r="46" spans="2:51" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B46" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C39" s="5">
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="5"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="5"/>
+      <c r="Q46" s="5"/>
+      <c r="R46" s="5"/>
+      <c r="S46" s="5"/>
+      <c r="T46" s="5"/>
+      <c r="U46" s="5"/>
+      <c r="V46" s="5"/>
+      <c r="W46" s="5"/>
+      <c r="X46" s="5"/>
+      <c r="Y46" s="5"/>
+      <c r="Z46" s="5">
         <v>38.009</v>
       </c>
-      <c r="D39" s="5">
+      <c r="AA46" s="5">
         <v>36.384999999999998</v>
       </c>
-      <c r="E39" s="5">
+      <c r="AB46" s="5">
         <v>37.402999999999999</v>
       </c>
-      <c r="F39" s="5">
+      <c r="AC46" s="5">
         <v>53.308</v>
       </c>
-      <c r="G39" s="5">
+      <c r="AD46" s="5">
         <v>44.9</v>
       </c>
-      <c r="H39" s="5">
+      <c r="AE46" s="5">
         <v>45.792000000000002</v>
       </c>
-      <c r="I39" s="5">
+      <c r="AF46" s="5">
         <v>53.11</v>
       </c>
-      <c r="J39" s="5">
+      <c r="AG46" s="5">
         <v>54.575000000000003</v>
       </c>
-      <c r="K39" s="5">
+      <c r="AH46" s="5">
         <v>58.066000000000003</v>
       </c>
-      <c r="L39" s="5">
+      <c r="AI46" s="5">
         <v>71.417000000000002</v>
       </c>
-      <c r="U39" s="1">
-        <f t="shared" si="6"/>
+      <c r="AX46" s="1">
+        <f t="shared" si="8"/>
         <v>165.10499999999999</v>
       </c>
     </row>
-    <row r="40" spans="2:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="3" t="s">
+    <row r="47" spans="2:51" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C40" s="4">
-        <f>C36-SUM(C37:C39)</f>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="4"/>
+      <c r="N47" s="4"/>
+      <c r="O47" s="4"/>
+      <c r="P47" s="4"/>
+      <c r="Q47" s="4"/>
+      <c r="R47" s="4"/>
+      <c r="S47" s="4"/>
+      <c r="T47" s="4"/>
+      <c r="U47" s="4"/>
+      <c r="V47" s="4"/>
+      <c r="W47" s="4"/>
+      <c r="X47" s="4"/>
+      <c r="Y47" s="4"/>
+      <c r="Z47" s="4">
+        <f t="shared" ref="Z47:AF47" si="9">Z43-SUM(Z44:Z46)</f>
         <v>-49.01700000000001</v>
       </c>
-      <c r="D40" s="4">
-        <f>D36-SUM(D37:D39)</f>
+      <c r="AA47" s="4">
+        <f t="shared" si="9"/>
         <v>-23.128000000000014</v>
       </c>
-      <c r="E40" s="4">
-        <f>E36-SUM(E37:E39)</f>
+      <c r="AB47" s="4">
+        <f t="shared" si="9"/>
         <v>-9.6059999999999945</v>
       </c>
-      <c r="F40" s="4">
-        <f>F36-SUM(F37:F39)</f>
+      <c r="AC47" s="4">
+        <f t="shared" si="9"/>
         <v>104.706</v>
       </c>
-      <c r="G40" s="4">
-        <f>G36-SUM(G37:G39)</f>
+      <c r="AD47" s="4">
+        <f t="shared" si="9"/>
         <v>-19.070000000000064</v>
       </c>
-      <c r="H40" s="4">
-        <f>H36-SUM(H37:H39)</f>
+      <c r="AE47" s="4">
+        <f t="shared" si="9"/>
         <v>-3.5029999999999575</v>
       </c>
-      <c r="I40" s="4">
-        <f>I36-SUM(I37:I39)</f>
+      <c r="AF47" s="4">
+        <f t="shared" si="9"/>
         <v>7.8459999999999468</v>
       </c>
-      <c r="J40" s="4">
-        <f t="shared" ref="J40:L40" si="7">J36-SUM(J37:J39)</f>
+      <c r="AG47" s="4">
+        <f t="shared" ref="AG47:AI47" si="10">AG43-SUM(AG44:AG46)</f>
         <v>87.528999999999996</v>
       </c>
-      <c r="K40" s="4">
-        <f t="shared" si="7"/>
+      <c r="AH47" s="4">
+        <f t="shared" si="10"/>
         <v>72.19</v>
       </c>
-      <c r="L40" s="4">
-        <f t="shared" si="7"/>
+      <c r="AI47" s="4">
+        <f t="shared" si="10"/>
         <v>182.23699999999999</v>
       </c>
-      <c r="U40" s="1">
-        <f t="shared" si="6"/>
+      <c r="AX47" s="1">
+        <f t="shared" si="8"/>
         <v>22.954999999999984</v>
       </c>
     </row>
-    <row r="41" spans="2:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="3" t="s">
+    <row r="48" spans="2:51" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B48" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="4"/>
-      <c r="L41" s="4"/>
-      <c r="U41" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B42" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="U42" s="1">
-        <f>SUM(C42:F42)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B43" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="U43" s="1">
-        <f t="shared" ref="U43:U46" si="8">SUM(C43:F43)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B44" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="U44" s="1">
+      <c r="AE48" s="4"/>
+      <c r="AF48" s="4"/>
+      <c r="AG48" s="4"/>
+      <c r="AH48" s="4"/>
+      <c r="AI48" s="4"/>
+      <c r="AX48" s="4">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="U45" s="1"/>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B46" t="s">
+    <row r="49" spans="2:50" x14ac:dyDescent="0.2">
+      <c r="B49" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AX49" s="1">
+        <f>SUM(Z49:AC49)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:50" x14ac:dyDescent="0.2">
+      <c r="B50" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="AX50" s="1">
+        <f>SUM(Z50:AC50)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:50" x14ac:dyDescent="0.2">
+      <c r="B51" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="AX51" s="1">
+        <f>SUM(Z51:AC51)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="2:50" x14ac:dyDescent="0.2">
+      <c r="AX52" s="1"/>
+    </row>
+    <row r="53" spans="2:50" x14ac:dyDescent="0.2">
+      <c r="B53" t="s">
         <v>45</v>
       </c>
-      <c r="C46" s="2">
-        <f>(C26-C32)/C26</f>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2"/>
+      <c r="L53" s="2"/>
+      <c r="M53" s="2"/>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" s="2"/>
+      <c r="Q53" s="2"/>
+      <c r="R53" s="2"/>
+      <c r="S53" s="2"/>
+      <c r="T53" s="2"/>
+      <c r="U53" s="2"/>
+      <c r="V53" s="2"/>
+      <c r="W53" s="2"/>
+      <c r="X53" s="2"/>
+      <c r="Y53" s="2"/>
+      <c r="Z53" s="2">
+        <f>(Z33-Z39)/Z33</f>
         <v>0.24521400067812524</v>
       </c>
-      <c r="D46" s="2">
-        <f t="shared" ref="D46:L46" si="9">(D26-D32)/D26</f>
+      <c r="AA53" s="2">
+        <f t="shared" ref="AA53:AI53" si="11">(AA33-AA39)/AA33</f>
         <v>0.28711313784753523</v>
       </c>
-      <c r="E46" s="2">
-        <f t="shared" si="9"/>
+      <c r="AB53" s="2">
+        <f t="shared" si="11"/>
         <v>0.33642469093553495</v>
       </c>
-      <c r="F46" s="2">
-        <f t="shared" si="9"/>
+      <c r="AC53" s="2">
+        <f t="shared" si="11"/>
         <v>0.46231060967414372</v>
       </c>
-      <c r="G46" s="2">
-        <f t="shared" si="9"/>
+      <c r="AD53" s="2">
+        <f t="shared" si="11"/>
         <v>0.34122972213962399</v>
       </c>
-      <c r="H46" s="2">
-        <f t="shared" si="9"/>
+      <c r="AE53" s="2">
+        <f t="shared" si="11"/>
         <v>0.32994393329984384</v>
       </c>
-      <c r="I46" s="2">
-        <f t="shared" si="9"/>
+      <c r="AF53" s="2">
+        <f t="shared" si="11"/>
         <v>0.35002628059347307</v>
       </c>
-      <c r="J46" s="2">
-        <f t="shared" si="9"/>
+      <c r="AG53" s="2">
+        <f t="shared" si="11"/>
         <v>0.3661139537688316</v>
       </c>
-      <c r="K46" s="2">
-        <f t="shared" si="9"/>
+      <c r="AH53" s="2">
+        <f t="shared" si="11"/>
         <v>0.34302699327157954</v>
       </c>
-      <c r="L46" s="2">
-        <f t="shared" si="9"/>
+      <c r="AI53" s="2">
+        <f t="shared" si="11"/>
         <v>0.36503234400206114</v>
       </c>
-      <c r="U46" s="4">
-        <f t="shared" si="8"/>
+      <c r="AX53" s="4">
+        <f>SUM(Z53:AC53)</f>
         <v>1.3310624391353392</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B47" t="s">
+    <row r="54" spans="2:50" x14ac:dyDescent="0.2">
+      <c r="B54" t="s">
         <v>46</v>
       </c>
-      <c r="C47" s="2">
-        <f t="shared" ref="C47:L49" si="10">(C27-C33)/C27</f>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2"/>
+      <c r="L54" s="2"/>
+      <c r="M54" s="2"/>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" s="2"/>
+      <c r="Q54" s="2"/>
+      <c r="R54" s="2"/>
+      <c r="S54" s="2"/>
+      <c r="T54" s="2"/>
+      <c r="U54" s="2"/>
+      <c r="V54" s="2"/>
+      <c r="W54" s="2"/>
+      <c r="X54" s="2"/>
+      <c r="Y54" s="2"/>
+      <c r="Z54" s="2">
+        <f t="shared" ref="Z54:AI56" si="12">(Z34-Z40)/Z34</f>
         <v>-0.34157637189793766</v>
       </c>
-      <c r="D47" s="2">
-        <f t="shared" si="10"/>
+      <c r="AA54" s="2">
+        <f t="shared" si="12"/>
         <v>-3.6622750567477241E-2</v>
       </c>
-      <c r="E47" s="2">
-        <f t="shared" si="10"/>
+      <c r="AB54" s="2">
+        <f t="shared" si="12"/>
         <v>-0.11344065892924007</v>
       </c>
-      <c r="F47" s="2">
-        <f t="shared" si="10"/>
+      <c r="AC54" s="2">
+        <f t="shared" si="12"/>
         <v>5.4919781650918549E-2</v>
       </c>
-      <c r="G47" s="2">
-        <f t="shared" si="10"/>
+      <c r="AD54" s="2">
+        <f t="shared" si="12"/>
         <v>9.9848444325578919E-3</v>
       </c>
-      <c r="H47" s="2">
-        <f t="shared" si="10"/>
+      <c r="AE54" s="2">
+        <f t="shared" si="12"/>
         <v>-2.279781654714751E-2</v>
       </c>
-      <c r="I47" s="2">
-        <f t="shared" si="10"/>
+      <c r="AF54" s="2">
+        <f t="shared" si="12"/>
         <v>8.8972678758761151E-2</v>
       </c>
-      <c r="J47" s="2">
-        <f t="shared" si="10"/>
+      <c r="AG54" s="2">
+        <f t="shared" si="12"/>
         <v>-0.10723629444642642</v>
       </c>
-      <c r="K47" s="2">
-        <f t="shared" si="10"/>
+      <c r="AH54" s="2">
+        <f t="shared" si="12"/>
         <v>-0.35282094790019658</v>
       </c>
-      <c r="L47" s="2">
-        <f t="shared" si="10"/>
+      <c r="AI54" s="2">
+        <f t="shared" si="12"/>
         <v>-3.6309780689709269E-2</v>
       </c>
     </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B48" t="s">
+    <row r="55" spans="2:50" x14ac:dyDescent="0.2">
+      <c r="B55" t="s">
         <v>47</v>
       </c>
-      <c r="C48" s="2">
-        <f t="shared" si="10"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2"/>
+      <c r="L55" s="2"/>
+      <c r="M55" s="2"/>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" s="2"/>
+      <c r="Q55" s="2"/>
+      <c r="R55" s="2"/>
+      <c r="S55" s="2"/>
+      <c r="T55" s="2"/>
+      <c r="U55" s="2"/>
+      <c r="V55" s="2"/>
+      <c r="W55" s="2"/>
+      <c r="X55" s="2"/>
+      <c r="Y55" s="2"/>
+      <c r="Z55" s="2">
+        <f t="shared" si="12"/>
         <v>-8.1473609635138817E-4</v>
       </c>
-      <c r="D48" s="2">
-        <f t="shared" si="10"/>
+      <c r="AA55" s="2">
+        <f t="shared" si="12"/>
         <v>2.4747292075154759E-3</v>
       </c>
-      <c r="E48" s="2">
-        <f t="shared" si="10"/>
+      <c r="AB55" s="2">
+        <f t="shared" si="12"/>
         <v>-1.1859498433836936E-2</v>
       </c>
-      <c r="F48" s="2">
-        <f t="shared" si="10"/>
+      <c r="AC55" s="2">
+        <f t="shared" si="12"/>
         <v>-1.6750325339282456E-2</v>
       </c>
-      <c r="G48" s="2">
-        <f t="shared" si="10"/>
+      <c r="AD55" s="2">
+        <f t="shared" si="12"/>
         <v>1.2885635317845761E-2</v>
       </c>
-      <c r="H48" s="2">
-        <f t="shared" si="10"/>
+      <c r="AE55" s="2">
+        <f t="shared" si="12"/>
         <v>9.2582049257102922E-2</v>
       </c>
-      <c r="I48" s="2">
-        <f t="shared" si="10"/>
+      <c r="AF55" s="2">
+        <f t="shared" si="12"/>
         <v>0.11556639991809846</v>
       </c>
-      <c r="J48" s="2">
-        <f t="shared" si="10"/>
+      <c r="AG55" s="2">
+        <f t="shared" si="12"/>
         <v>0.16861454669238626</v>
       </c>
-      <c r="K48" s="2">
-        <f t="shared" si="10"/>
+      <c r="AH55" s="2">
+        <f t="shared" si="12"/>
         <v>0.13275909436157657</v>
       </c>
-      <c r="L48" s="2">
-        <f t="shared" si="10"/>
+      <c r="AI55" s="2">
+        <f t="shared" si="12"/>
         <v>0.1865320255566984</v>
       </c>
     </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B49" t="s">
+    <row r="56" spans="2:50" x14ac:dyDescent="0.2">
+      <c r="B56" t="s">
         <v>48</v>
       </c>
-      <c r="C49" s="2">
-        <f t="shared" si="10"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
+      <c r="L56" s="2"/>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" s="2"/>
+      <c r="Q56" s="2"/>
+      <c r="R56" s="2"/>
+      <c r="S56" s="2"/>
+      <c r="T56" s="2"/>
+      <c r="U56" s="2"/>
+      <c r="V56" s="2"/>
+      <c r="W56" s="2"/>
+      <c r="X56" s="2"/>
+      <c r="Y56" s="2"/>
+      <c r="Z56" s="2">
+        <f t="shared" si="12"/>
         <v>0.31532430506058445</v>
       </c>
-      <c r="D49" s="2">
-        <f t="shared" si="10"/>
+      <c r="AA56" s="2">
+        <f t="shared" si="12"/>
         <v>0.35089820359281437</v>
       </c>
-      <c r="E49" s="2">
-        <f t="shared" si="10"/>
+      <c r="AB56" s="2">
+        <f t="shared" si="12"/>
         <v>0.31534521318808167</v>
       </c>
-      <c r="F49" s="2">
-        <f t="shared" si="10"/>
+      <c r="AC56" s="2">
+        <f t="shared" si="12"/>
         <v>1.4718133851707923E-2</v>
       </c>
-      <c r="G49" s="2">
-        <f t="shared" si="10"/>
+      <c r="AD56" s="2">
+        <f t="shared" si="12"/>
         <v>0.57080844432901723</v>
       </c>
-      <c r="H49" s="2">
-        <f t="shared" si="10"/>
+      <c r="AE56" s="2">
+        <f t="shared" si="12"/>
         <v>0.39570647931303676</v>
       </c>
-      <c r="I49" s="2">
-        <f t="shared" si="10"/>
+      <c r="AF56" s="2">
+        <f t="shared" si="12"/>
         <v>0.43751207262893566</v>
       </c>
-      <c r="J49" s="2">
-        <f t="shared" si="10"/>
+      <c r="AG56" s="2">
+        <f t="shared" si="12"/>
         <v>0.28808755985536988</v>
       </c>
-      <c r="K49" s="2">
-        <f t="shared" si="10"/>
+      <c r="AH56" s="2">
+        <f t="shared" si="12"/>
         <v>0.23868229587712214</v>
       </c>
-      <c r="L49" s="2">
-        <f t="shared" si="10"/>
+      <c r="AI56" s="2">
+        <f t="shared" si="12"/>
         <v>0.31072254044819619</v>
       </c>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B51" t="s">
+    <row r="58" spans="2:50" x14ac:dyDescent="0.2">
+      <c r="B58" t="s">
         <v>23</v>
       </c>
-      <c r="C51" s="2">
-        <f t="shared" ref="C51:F51" si="11">C36/C30</f>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2"/>
+      <c r="L58" s="2"/>
+      <c r="M58" s="2"/>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" s="2"/>
+      <c r="Q58" s="2"/>
+      <c r="R58" s="2"/>
+      <c r="S58" s="2"/>
+      <c r="T58" s="2"/>
+      <c r="U58" s="2"/>
+      <c r="V58" s="2"/>
+      <c r="W58" s="2"/>
+      <c r="X58" s="2"/>
+      <c r="Y58" s="2"/>
+      <c r="Z58" s="2">
+        <f t="shared" ref="Z58" si="13">Z43/Z37</f>
         <v>0.16182032996455556</v>
       </c>
-      <c r="D51" s="2">
-        <f>D36/D30</f>
+      <c r="AA58" s="2">
+        <f>AA43/AA37</f>
         <v>0.20407604082592987</v>
       </c>
-      <c r="E51" s="2">
-        <f t="shared" ref="E51:F51" si="12">E36/E30</f>
+      <c r="AB58" s="2">
+        <f t="shared" ref="AB58:AC58" si="14">AB43/AB37</f>
         <v>0.23840348137657211</v>
       </c>
-      <c r="F51" s="2">
-        <f t="shared" si="12"/>
+      <c r="AC58" s="2">
+        <f t="shared" si="14"/>
         <v>0.38315807495898796</v>
       </c>
-      <c r="G51" s="2">
-        <f>G36/G30</f>
+      <c r="AD58" s="2">
+        <f>AD43/AD37</f>
         <v>0.2720898347038993</v>
       </c>
-      <c r="H51" s="2">
-        <f>H36/H30</f>
+      <c r="AE58" s="2">
+        <f>AE43/AE37</f>
         <v>0.26697853165919827</v>
       </c>
-      <c r="I51" s="2">
-        <f>I36/I30</f>
+      <c r="AF58" s="2">
+        <f>AF43/AF37</f>
         <v>0.2922176754365684</v>
       </c>
-      <c r="J51" s="2">
-        <f>J36/J30</f>
+      <c r="AG58" s="2">
+        <f>AG43/AG37</f>
         <v>0.30847401833394839</v>
       </c>
-      <c r="K51" s="2">
-        <f t="shared" ref="K51:L51" si="13">K36/K30</f>
+      <c r="AH58" s="2">
+        <f t="shared" ref="AH58:AI58" si="15">AH43/AH37</f>
         <v>0.30030330708577546</v>
       </c>
-      <c r="L51" s="2">
-        <f t="shared" si="13"/>
+      <c r="AI58" s="2">
+        <f t="shared" si="15"/>
         <v>0.33375603666349091</v>
       </c>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B52" t="s">
+    <row r="59" spans="2:50" x14ac:dyDescent="0.2">
+      <c r="B59" t="s">
         <v>25</v>
       </c>
-      <c r="C52" s="2">
-        <f t="shared" ref="C52:F52" si="14">C40/C30</f>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2"/>
+      <c r="L59" s="2"/>
+      <c r="M59" s="2"/>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" s="2"/>
+      <c r="Q59" s="2"/>
+      <c r="R59" s="2"/>
+      <c r="S59" s="2"/>
+      <c r="T59" s="2"/>
+      <c r="U59" s="2"/>
+      <c r="V59" s="2"/>
+      <c r="W59" s="2"/>
+      <c r="X59" s="2"/>
+      <c r="Y59" s="2"/>
+      <c r="Z59" s="2">
+        <f t="shared" ref="Z59" si="16">Z47/Z37</f>
         <v>-0.20831881273958983</v>
       </c>
-      <c r="D52" s="2">
-        <f>D40/D30</f>
+      <c r="AA59" s="2">
+        <f>AA47/AA37</f>
         <v>-6.8881099095503773E-2</v>
       </c>
-      <c r="E52" s="2">
-        <f t="shared" ref="E52:F52" si="15">E40/E30</f>
+      <c r="AB59" s="2">
+        <f t="shared" ref="AB59:AC59" si="17">AB47/AB37</f>
         <v>-2.9069978574281858E-2</v>
       </c>
-      <c r="F52" s="2">
-        <f t="shared" si="15"/>
+      <c r="AC59" s="2">
+        <f t="shared" si="17"/>
         <v>0.18292676535177754</v>
       </c>
-      <c r="G52" s="2">
-        <f>G40/G30</f>
+      <c r="AD59" s="2">
+        <f>AD47/AD37</f>
         <v>-5.8493164550750001E-2</v>
       </c>
-      <c r="H52" s="2">
-        <f>H40/H30</f>
+      <c r="AE59" s="2">
+        <f>AE47/AE37</f>
         <v>-8.7303921324287017E-3</v>
       </c>
-      <c r="I52" s="2">
-        <f>I40/I30</f>
+      <c r="AF59" s="2">
+        <f>AF47/AF37</f>
         <v>1.5116135694579204E-2</v>
       </c>
-      <c r="J52" s="2">
-        <f>J40/J30</f>
+      <c r="AG59" s="2">
+        <f>AG47/AG37</f>
         <v>0.11255100085767594</v>
       </c>
-      <c r="K52" s="2">
-        <f t="shared" ref="K52:L52" si="16">K40/K30</f>
+      <c r="AH59" s="2">
+        <f t="shared" ref="AH59:AI59" si="18">AH47/AH37</f>
         <v>9.6118255145435622E-2</v>
       </c>
-      <c r="L52" s="2">
-        <f t="shared" si="16"/>
+      <c r="AI59" s="2">
+        <f t="shared" si="18"/>
         <v>0.17105592918858795</v>
+      </c>
+    </row>
+    <row r="62" spans="2:50" x14ac:dyDescent="0.2">
+      <c r="B62" t="s">
+        <v>3</v>
+      </c>
+      <c r="C62">
+        <f>91.596-C63</f>
+        <v>65.736000000000004</v>
+      </c>
+    </row>
+    <row r="63" spans="2:50" x14ac:dyDescent="0.2">
+      <c r="B63" t="s">
+        <v>119</v>
+      </c>
+      <c r="C63">
+        <v>25.86</v>
+      </c>
+    </row>
+    <row r="64" spans="2:50" x14ac:dyDescent="0.2">
+      <c r="B64" t="s">
+        <v>120</v>
+      </c>
+      <c r="C64">
+        <v>15.702999999999999</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B65" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B66" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B67" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B68" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B69" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B70" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B71" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B72" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B73" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B75" s="12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B76" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B77" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B78" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B79" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B80" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B81" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B82" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B83" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B84" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B85" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B86" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B87" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B88" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B89" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B90" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="91" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B91" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="92" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B92" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B93" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B94" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="95" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B95" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B96" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B97" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B98" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B99" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B100" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B101" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B102" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B103" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B104" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B105" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B106" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B107" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B108" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" xr:uid="{1FAF2979-6CF6-6744-A115-04A73A693658}"/>
-    <hyperlink ref="J2" r:id="rId2" xr:uid="{B4460851-C963-AB4A-B74B-B1543837C523}"/>
-    <hyperlink ref="L2" r:id="rId3" xr:uid="{27D2C943-0735-7A4F-B963-EB4B8E1539BC}"/>
-    <hyperlink ref="K2" r:id="rId4" xr:uid="{BAA97FB5-CBF8-234C-9C9D-BEE8555D357E}"/>
-    <hyperlink ref="G2" r:id="rId5" xr:uid="{AA46C004-351A-B148-8189-3893B1839AE1}"/>
-    <hyperlink ref="F2" r:id="rId6" xr:uid="{474162AE-A699-1E48-A739-CFC4950119C5}"/>
-    <hyperlink ref="E2" r:id="rId7" xr:uid="{C3C3D541-4922-1E45-80F1-A0BDF8193A40}"/>
+    <hyperlink ref="AE2" r:id="rId1" xr:uid="{1FAF2979-6CF6-6744-A115-04A73A693658}"/>
+    <hyperlink ref="AG2" r:id="rId2" xr:uid="{B4460851-C963-AB4A-B74B-B1543837C523}"/>
+    <hyperlink ref="AI2" r:id="rId3" xr:uid="{27D2C943-0735-7A4F-B963-EB4B8E1539BC}"/>
+    <hyperlink ref="AH2" r:id="rId4" xr:uid="{BAA97FB5-CBF8-234C-9C9D-BEE8555D357E}"/>
+    <hyperlink ref="AD2" r:id="rId5" xr:uid="{AA46C004-351A-B148-8189-3893B1839AE1}"/>
+    <hyperlink ref="AC2" r:id="rId6" xr:uid="{474162AE-A699-1E48-A739-CFC4950119C5}"/>
+    <hyperlink ref="AB2" r:id="rId7" xr:uid="{C3C3D541-4922-1E45-80F1-A0BDF8193A40}"/>
+    <hyperlink ref="I2" r:id="rId8" display="Q424" xr:uid="{23BABA5E-3B73-2140-BE4D-3B2D1807894E}"/>
+    <hyperlink ref="H2" r:id="rId9" display="Q324" xr:uid="{46F02845-6A11-E14C-89DB-90C9E1AE7248}"/>
+    <hyperlink ref="M2" r:id="rId10" display="Q424" xr:uid="{D07F38D8-C2F0-1747-B94F-B6E81665FAB0}"/>
+    <hyperlink ref="L2" r:id="rId11" display="Q324" xr:uid="{D56F5B68-0CBB-4E4B-9734-DBEA10A799D8}"/>
+    <hyperlink ref="Q2" r:id="rId12" display="Q424" xr:uid="{481602D4-2691-E249-ABB4-DA56016D9CF0}"/>
+    <hyperlink ref="P2" r:id="rId13" display="Q324" xr:uid="{70B3A524-CA7B-374A-9E62-985AEBEDE01A}"/>
+    <hyperlink ref="U2" r:id="rId14" display="Q424" xr:uid="{585182FE-B5FF-B340-A288-91545D352F05}"/>
+    <hyperlink ref="T2" r:id="rId15" display="Q324" xr:uid="{738EDA3E-5CCB-854E-A25C-15796D2BA056}"/>
+    <hyperlink ref="E2" r:id="rId16" display="Q424" xr:uid="{E19F3570-146D-654A-B04C-C8EA95F4DF4A}"/>
+    <hyperlink ref="D2" r:id="rId17" display="Q324" xr:uid="{7AA6C1EA-0B58-5446-997B-A9869003E23C}"/>
+    <hyperlink ref="C2" r:id="rId18" xr:uid="{A742DC59-185A-4340-AA1B-877B38C1C6EC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId8"/>
-  <legacyDrawing r:id="rId9"/>
+  <drawing r:id="rId19"/>
+  <legacyDrawing r:id="rId20"/>
 </worksheet>
 </file>
--- a/BE.xlsx
+++ b/BE.xlsx
@@ -12,159 +12,6 @@
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>VAE Ventures</author>
-  </authors>
-  <commentList>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{ADE44D27-8ED5-8546-9775-6A086F0F5ABA}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>VAE Ventures:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>High temperature solid oxide fuel cell (fuel -&gt; electriicity)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K6" authorId="0" shapeId="0" xr:uid="{B5D4356B-75F9-B34D-8DB5-2815F3145C0D}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>VAE Ventures:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Investments in unconsolidated affiliates...</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Dillon Walton</author>
-    <author>VAE Ventures</author>
-  </authors>
-  <commentList>
-    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{5F610A5F-D63B-214C-A148-F86F272D8AFC}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Dillon Walton:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Out of backlog -&gt; into production, producing for 24 hrs</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B18" authorId="1" shapeId="0" xr:uid="{A9D2441D-108E-2747-91C5-0397C0B969E2}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>VAE Ventures:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Began operations in 2018</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>

--- a/BE.xlsx
+++ b/BE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{589885C6-8FAA-4CCD-9255-8B4F73D235C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3690358-D56D-4B2F-BD7C-7452CE9AE711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{A9783F60-192C-EF49-B653-EB874A40C134}"/>
   </bookViews>
@@ -193,7 +193,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="125">
   <si>
     <t>Price</t>
   </si>
@@ -564,13 +564,19 @@
   </si>
   <si>
     <t>Quarter</t>
+  </si>
+  <si>
+    <t>10-Q</t>
+  </si>
+  <si>
+    <t>10-K</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -636,6 +642,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -664,7 +678,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -685,6 +699,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -710,30 +725,75 @@
       <xdr:col>35</xdr:col>
       <xdr:colOff>25400</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>35</xdr:col>
       <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="3" name="Straight Arrow Connector 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B24FF4BD-3A17-5991-8733-E085913DD518}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9105900" y="114300"/>
-          <a:ext cx="0" cy="7137400"/>
-        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>51</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>51</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Straight Arrow Connector 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
         </a:prstGeom>
@@ -1315,12 +1375,113 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1997143C-4B46-1145-8926-BC951BDCF94E}">
-  <dimension ref="B2:BN108"/>
+  <dimension ref="B1:BN108"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="2:66" x14ac:dyDescent="0.25">
+      <c r="C1" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="M1" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="N1" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="O1" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="P1" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q1" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="R1" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="S1" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="T1" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="U1" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="V1" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="W1" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="X1" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y1" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z1" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="AA1" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB1" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="AC1" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="AD1" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE1" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="AF1" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="AG1" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="AH1" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="AI1" s="14" t="s">
+        <v>123</v>
+      </c>
+    </row>
     <row r="2" spans="2:66" x14ac:dyDescent="0.25">
       <c r="C2" s="10" t="s">
         <v>93</v>
@@ -3579,9 +3740,42 @@
     <hyperlink ref="Z2" r:id="rId31" display="https://www.sec.gov/Archives/edgar/data/1664703/000162828024022195/ex991_q12024financialresul.htm" xr:uid="{16BFFBC5-548E-47A0-A128-0EB77A06A1EE}"/>
     <hyperlink ref="AA2" r:id="rId32" display="https://www.sec.gov/Archives/edgar/data/1664703/000162828024036108/ex991_q22024financialresul.htm" xr:uid="{B831AF90-CBEC-424D-BF0A-6B0C66957509}"/>
     <hyperlink ref="AF2" r:id="rId33" display="https://www.sec.gov/Archives/edgar/data/1664703/000162828025046745/ex991_q32025financialresul.htm" xr:uid="{86E07AD2-A9B1-4216-B6E4-70DBED65193E}"/>
+    <hyperlink ref="C1" r:id="rId34" display="https://www.sec.gov/Archives/edgar/data/1664703/000162828018011710/bloomenergycorp6-30x1810q.htm" xr:uid="{07D46E88-50D7-4347-8B4C-28C251B987D4}"/>
+    <hyperlink ref="D1" r:id="rId35" display="https://www.sec.gov/Archives/edgar/data/1664703/000162828018014294/a2018q310qbloomenergycorp.htm" xr:uid="{B3FA7D40-3ADD-44DB-BEED-F86B999FB338}"/>
+    <hyperlink ref="E1" r:id="rId36" display="https://www.sec.gov/Archives/edgar/data/1664703/000166470319000008/a2018q410kbloomenergycorp.htm" xr:uid="{E6A8F29B-BC65-4560-B5B7-C23BAF0F052C}"/>
+    <hyperlink ref="F1" r:id="rId37" display="https://www.sec.gov/Archives/edgar/data/1664703/000166470319000014/a2019q110qbloomenergycorp.htm" xr:uid="{27721836-F6F6-4D10-8C17-A2763FD5C0BF}"/>
+    <hyperlink ref="G1" r:id="rId38" display="https://www.sec.gov/Archives/edgar/data/1664703/000166470319000025/a2019_q2x10qxbloomenergyv4.htm" xr:uid="{8734A325-3AD6-42DB-8734-21AA626468B9}"/>
+    <hyperlink ref="H1" r:id="rId39" display="https://www.sec.gov/Archives/edgar/data/1664703/000166470319000040/a2019_q3x10qxbloomenergy.htm" xr:uid="{3691970F-267C-4116-B770-9E6725FEDCDB}"/>
+    <hyperlink ref="I1" r:id="rId40" display="https://www.sec.gov/Archives/edgar/data/1664703/000166470320000013/a2019q410kbloom.htm" xr:uid="{51420E23-8C46-413B-B868-98DE1F4381F4}"/>
+    <hyperlink ref="J1" r:id="rId41" display="https://www.sec.gov/Archives/edgar/data/1664703/000166470320000037/a2020q110qbloomd47.htm" xr:uid="{75E659BD-BBD4-401F-976D-34DBB87358BB}"/>
+    <hyperlink ref="K1" r:id="rId42" display="https://www.sec.gov/Archives/edgar/data/1664703/000166470320000057/be-20200630.htm" xr:uid="{24FB3F61-6328-44A4-889E-4ED8C92F57B8}"/>
+    <hyperlink ref="L1" r:id="rId43" display="https://www.sec.gov/Archives/edgar/data/1664703/000166470320000080/be-20200930.htm" xr:uid="{327EF0DF-317C-4191-92D2-C487AE204504}"/>
+    <hyperlink ref="M1" r:id="rId44" display="https://www.sec.gov/Archives/edgar/data/1664703/000166470321000017/be-20201231.htm" xr:uid="{6EF26663-F04B-449E-9270-26E4B9AE719D}"/>
+    <hyperlink ref="N1" r:id="rId45" display="https://www.sec.gov/Archives/edgar/data/1664703/000166470321000046/be-20210331.htm" xr:uid="{6B855EA7-555F-4829-ACD0-7E6DEBF942AB}"/>
+    <hyperlink ref="O1" r:id="rId46" display="https://www.sec.gov/Archives/edgar/data/1664703/000166470321000135/be-20210630.htm" xr:uid="{603CC064-ECF4-4A7A-B829-38931A604DA9}"/>
+    <hyperlink ref="P1" r:id="rId47" display="https://www.sec.gov/Archives/edgar/data/1664703/000166470321000172/be-20210930.htm" xr:uid="{8268B1E8-7BC7-42E7-9F89-E2243F3B8B65}"/>
+    <hyperlink ref="Q1" r:id="rId48" display="https://www.sec.gov/Archives/edgar/data/1664703/000166470322000034/be-20211231.htm" xr:uid="{1EE137D7-B68A-46AD-B56B-5E5D02BEA78C}"/>
+    <hyperlink ref="R1" r:id="rId49" display="https://www.sec.gov/Archives/edgar/data/1664703/000166470322000059/be-20220331.htm" xr:uid="{81D1B0AB-8DC8-4271-8441-F02CF6A14A13}"/>
+    <hyperlink ref="S1" r:id="rId50" display="https://www.sec.gov/Archives/edgar/data/1664703/000166470322000068/be-20220630.htm" xr:uid="{0C18B066-6B56-44A9-8C2D-FCEC6A2EF4C2}"/>
+    <hyperlink ref="T1" r:id="rId51" display="https://www.sec.gov/Archives/edgar/data/1664703/000162828022028193/be-20220930.htm" xr:uid="{8A153307-D18B-4C76-94F3-228079C34165}"/>
+    <hyperlink ref="U1" r:id="rId52" display="https://www.sec.gov/Archives/edgar/data/1664703/000162828023004301/be-20221231.htm" xr:uid="{A291DDAC-D8F1-4955-9702-4222518994BF}"/>
+    <hyperlink ref="V1" r:id="rId53" display="https://www.sec.gov/Archives/edgar/data/1664703/000162828023016818/be-20230331.htm" xr:uid="{6B67DCA8-5776-437B-BF4D-7EB903B0F55A}"/>
+    <hyperlink ref="W1" r:id="rId54" display="https://www.sec.gov/Archives/edgar/data/1664703/000162828023027213/be-20230630.htm" xr:uid="{9F029597-F1C8-4B31-86C2-7A3DA45AB692}"/>
+    <hyperlink ref="X1" r:id="rId55" display="https://www.sec.gov/Archives/edgar/data/1664703/000162828023037836/be-20230930.htm" xr:uid="{A38CA5BD-AC65-434F-81B0-75D4FD3F535B}"/>
+    <hyperlink ref="Y1" r:id="rId56" display="https://www.sec.gov/Archives/edgar/data/1664703/000162828024005035/be-20231231.htm" xr:uid="{BC4322FC-21FF-4786-BD55-9D0390135467}"/>
+    <hyperlink ref="Z1" r:id="rId57" display="https://www.sec.gov/Archives/edgar/data/1664703/000162828024022309/be-20240331.htm" xr:uid="{B1EE9AAB-3784-4A4E-A518-7FC3D86EFE12}"/>
+    <hyperlink ref="AA1" r:id="rId58" display="https://www.sec.gov/Archives/edgar/data/1664703/000162828024036219/be-20240630.htm" xr:uid="{460C38AB-C93A-44E2-BAEA-CB37F4CBF5A0}"/>
+    <hyperlink ref="AB1" r:id="rId59" display="https://www.sec.gov/Archives/edgar/data/1664703/000162828024046411/be-20240930.htm" xr:uid="{1A6B56CA-62FD-4DBC-AA75-5988412B68CF}"/>
+    <hyperlink ref="AC1" r:id="rId60" display="https://www.sec.gov/Archives/edgar/data/1664703/000162828025008747/be-20241231.htm" xr:uid="{D8C09D67-C675-471D-8CEF-99CADB71950B}"/>
+    <hyperlink ref="AD1" r:id="rId61" display="https://www.sec.gov/Archives/edgar/data/1664703/000162828025021160/be-20250331.htm" xr:uid="{7716CF89-E53F-4989-8ECF-3801A4CEFF02}"/>
+    <hyperlink ref="AE1" r:id="rId62" display="https://www.sec.gov/Archives/edgar/data/1664703/000162828025037074/be-20250630.htm" xr:uid="{4BD674A1-F4C1-42FE-926E-38B51695F690}"/>
+    <hyperlink ref="AF1" r:id="rId63" display="https://www.sec.gov/Archives/edgar/data/1664703/000162828025046844/be-20250930.htm" xr:uid="{882048DA-48A7-459C-8B54-874BFDD5734E}"/>
+    <hyperlink ref="AG1" r:id="rId64" display="https://www.sec.gov/Archives/edgar/data/1664703/000162828026006516/be-20251231.htm" xr:uid="{3029142E-CDC2-4817-B9D7-63625BE13BF0}"/>
+    <hyperlink ref="AH1" r:id="rId65" display="https://www.sec.gov/Archives/edgar/data/1664703/000162828026028021/be-20260331.htm" xr:uid="{6081357D-DE53-43FE-AB8F-35A4E9B5737B}"/>
+    <hyperlink ref="AI1" r:id="rId66" display="https://www.sec.gov/Archives/edgar/data/1664703/000162828026050247/be-20260630.htm" xr:uid="{FA3CAEF7-13CC-4C8C-82AA-1DB96504733B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId34"/>
-  <legacyDrawing r:id="rId35"/>
+  <drawing r:id="rId67"/>
+  <legacyDrawing r:id="rId68"/>
 </worksheet>
 </file>